--- a/output/第10期計画素案_修正指示書_令和8年7月.xlsx
+++ b/output/第10期計画素案_修正指示書_令和8年7月.xlsx
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>交付金評価の指標群別得点で、成果指標群が全国の123.5％である一方、活動指標群は推進で全国の23.2％、支援で55.6％にとどまる。「結果は出ているが、その結果を生んだ活動を国の様式で記録・報告できていない」状態であり、第9期計画の第5章がアウトプット指標を持たないこと（A-18）を国の評価が独立に裏付けている。</t>
+          <t>交付金評価の指標群別得点で、成果指標群が全国の123.5％である一方、活動指標群は推進で全国の23.2％、支援で55.6％にとどまる。成果と活動の得点に差がある状態（原因は評価調書の受領後に確認）であり、第9期計画の第5章がアウトプット指標を持たないこと（A-18）を国の評価が独立に裏付けている。</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
